--- a/july 2026/GT_JULY_26/22-07-2026/Umair.xlsx
+++ b/july 2026/GT_JULY_26/22-07-2026/Umair.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45933B74-3D7C-40A6-8F61-0AB71E5F9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47BAB43-6FB9-4B93-8F1D-4E425DBCAAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="141">
   <si>
     <t>Gm</t>
   </si>
@@ -455,6 +455,18 @@
   </si>
   <si>
     <t xml:space="preserve">Customer Name : Alhamd Bakers </t>
+  </si>
+  <si>
+    <t>352001409541-9</t>
+  </si>
+  <si>
+    <t>352013014458-1</t>
+  </si>
+  <si>
+    <t>issu</t>
+  </si>
+  <si>
+    <t>return</t>
   </si>
 </sst>
 </file>
@@ -3266,7 +3278,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -3294,7 +3306,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -3934,37 +3946,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="104">
         <f>I22*8.6%</f>
-        <v>134.9512</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1355.7888000000003</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>244.04198400000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>7.9991539200000012</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1607.8299379200002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4094,36 +4104,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>7380.4</v>
+        <v>5811.2</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>338.34320000000002</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>543.35599999999999</v>
+        <v>464.89600000000002</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>6498.7008000000005</v>
+        <v>5142.9120000000003</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1169.7661439999999</v>
+        <v>925.72415999999998</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>38.342334719999997</v>
+        <v>30.343180799999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>7706.8092787200003</v>
+        <v>6098.9793407999996</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4173,7 +4183,7 @@
       <c r="O28" s="231"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>7380.4</v>
+        <v>5811.2</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4194,7 +4204,7 @@
       <c r="O29" s="233"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>543.35599999999999</v>
+        <v>464.89600000000002</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4215,7 +4225,7 @@
       <c r="O30" s="233"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>338.34320000000002</v>
+        <v>203.39200000000002</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4237,7 +4247,7 @@
       <c r="O31" s="233"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>6498.7007999999996</v>
+        <v>5142.9120000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4262,7 +4272,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1169.7661439999999</v>
+        <v>925.72415999999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4284,7 +4294,7 @@
       <c r="O33" s="235"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>7668.4669439999998</v>
+        <v>6068.63616</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4309,7 +4319,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>38.342334719999997</v>
+        <v>30.343180799999999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4319,7 +4329,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>7706.8092787199994</v>
+        <v>6098.9793407999996</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4491,7 +4501,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -4519,7 +4529,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -4985,37 +4995,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>6</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>15.254400000000002</v>
+        <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>385.71840000000003</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>69.429311999999996</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>11.378692800000001</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>466.52640480000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5043,37 +5051,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>6</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J20" s="117"/>
       <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>15.254400000000002</v>
+        <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>385.71840000000003</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>69.429311999999996</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>11.378692800000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>466.52640480000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5101,37 +5107,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>6</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>15.254400000000002</v>
+        <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>385.71840000000003</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>69.429311999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>11.378692800000001</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>466.52640480000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5317,36 +5321,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1307.52</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>45.763200000000005</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>104.60160000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1157.1552000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>208.287936</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>34.136078400000002</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1399.5792144000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5396,7 +5400,7 @@
       <c r="O28" s="231"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1307.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5417,7 +5421,7 @@
       <c r="O29" s="233"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>104.60160000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5438,7 +5442,7 @@
       <c r="O30" s="233"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>45.763200000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5460,7 +5464,7 @@
       <c r="O31" s="233"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1157.1551999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5485,7 +5489,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>208.287936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5507,7 +5511,7 @@
       <c r="O33" s="235"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1365.4431359999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5532,7 +5536,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>34.136078399999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5542,7 +5546,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1399.5792144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5714,7 +5718,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -5742,7 +5746,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -5834,7 +5838,9 @@
       <c r="A10" s="236" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="191"/>
+      <c r="B10" s="191" t="s">
+        <v>138</v>
+      </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
@@ -5857,11 +5863,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="236"/>
       <c r="B11" s="76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -5998,7 +6004,7 @@
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" s="94" t="s">
         <v>1</v>
@@ -6058,11 +6064,11 @@
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>13.6966471875</v>
+        <v>2.7393294374999999</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>561.56253468750003</v>
+        <v>550.60521693750002</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -6120,11 +6126,11 @@
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>13.6966471875</v>
+        <v>2.7393294374999999</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>561.56253468750003</v>
+        <v>550.60521693750002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -6563,11 +6569,11 @@
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>27.393294375</v>
+        <v>5.4786588749999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1123.1250693750001</v>
+        <v>1101.210433875</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6749,11 +6755,11 @@
       </c>
       <c r="O34" s="159">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>27.393294375</v>
+        <v>5.4786588749999998</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6763,7 +6769,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1123.1250693750001</v>
+        <v>1101.210433875</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6935,7 +6941,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -6963,7 +6969,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -8156,7 +8162,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -8184,7 +8190,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -9373,7 +9379,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -9401,7 +9407,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -10590,7 +10596,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -10618,7 +10624,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -11807,7 +11813,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -11835,7 +11841,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -13024,7 +13030,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -13052,7 +13058,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -14241,7 +14247,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -14269,7 +14275,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -18208,7 +18214,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -18236,7 +18242,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -19425,7 +19431,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -19453,7 +19459,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -20642,7 +20648,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -20670,7 +20676,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -21859,7 +21865,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -21887,7 +21893,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -23078,7 +23084,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -23106,7 +23112,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -23370,7 +23376,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>245.97398304000001</v>
+        <v>0</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23431,11 +23437,11 @@
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>13.6966471875</v>
+        <v>2.7393294374999999</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>561.56253468750003</v>
+        <v>550.60521693750002</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23450,7 +23456,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="109" t="s">
         <v>25</v>
       </c>
@@ -23505,11 +23511,11 @@
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>13.6966471875</v>
+        <v>2.7393294374999999</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>561.56253468750003</v>
+        <v>550.60521693750002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23518,13 +23524,13 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>1639.8265536000001</v>
+        <v>0</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="109" t="s">
         <v>23</v>
       </c>
@@ -23594,7 +23600,7 @@
         <v>245.97398304000001</v>
       </c>
     </row>
-    <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="109" t="s">
         <v>33</v>
       </c>
@@ -23621,11 +23627,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>2760.32</v>
+        <v>2324.48</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19</f>
@@ -23633,27 +23639,27 @@
       </c>
       <c r="K19" s="171">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>96.611200000000011</v>
+        <v>81.356800000000007</v>
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>220.82560000000001</v>
+        <v>185.95840000000001</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>2442.8832000000002</v>
+        <v>2057.1648</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>470.57644800000003</v>
+        <v>401.14713600000005</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>23.670252480000002</v>
+        <v>12.291559679999999</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>2937.1299004799998</v>
+        <v>2470.6034956799999</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23661,10 +23667,10 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>1639.8265536000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+        <v>1607.8299379200002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="109" t="s">
         <v>31</v>
       </c>
@@ -23691,11 +23697,11 @@
       <c r="G20" s="114"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>4794.24</v>
+        <v>4358.3999999999996</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20</f>
@@ -23703,27 +23709,27 @@
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>167.79840000000002</v>
+        <v>152.54400000000001</v>
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>383.53920000000005</v>
+        <v>348.67200000000003</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>4242.9023999999999</v>
+        <v>3857.1839999999997</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>763.72243200000003</v>
+        <v>694.29312000000004</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>34.136078400000002</v>
+        <v>22.757385599999999</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>5040.7609103999994</v>
+        <v>4574.2345055999995</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23731,10 +23737,10 @@
       </c>
       <c r="U20" s="164">
         <f>+'7'!P35</f>
-        <v>7706.8092787199994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+        <v>6098.9793407999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="109" t="s">
         <v>29</v>
       </c>
@@ -23761,11 +23767,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21</f>
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>4213.12</v>
+        <v>3777.28</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21</f>
@@ -23773,27 +23779,27 @@
       </c>
       <c r="K21" s="171">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>147.45920000000001</v>
+        <v>132.20480000000001</v>
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>337.0496</v>
+        <v>302.18240000000003</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>3728.6111999999998</v>
+        <v>3342.8928000000001</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>702.00748799999997</v>
+        <v>632.57817599999998</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>31.256047680000002</v>
+        <v>19.877354879999999</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>4461.8747356799995</v>
+        <v>3995.34833088</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23801,10 +23807,16 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>1399.5792144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="109" t="s">
         <v>35</v>
       </c>
@@ -23831,11 +23843,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="171">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22+'17'!H22+'18'!H22+'19'!H22+'20'!H22</f>
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>8316.76</v>
+        <v>4942.9800000000005</v>
       </c>
       <c r="J22" s="171">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22+'19'!J22+'20'!J22</f>
@@ -23843,27 +23855,27 @@
       </c>
       <c r="K22" s="171">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>715.24135999999999</v>
+        <v>425.09627999999998</v>
       </c>
       <c r="L22" s="174">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>415.83800000000014</v>
+        <v>247.14900000000006</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>7185.6806400000005</v>
+        <v>4270.7347200000004</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>1293.4225152000001</v>
+        <v>768.73224960000016</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>115.98773184000004</v>
+        <v>29.996827200000006</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>8595.0908870399999</v>
+        <v>5069.4637967999997</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -23871,10 +23883,27 @@
       </c>
       <c r="U22" s="164">
         <f>+'9'!P35</f>
-        <v>1123.1250693750001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
+        <v>1101.210433875</v>
+      </c>
+      <c r="W22">
+        <v>394</v>
+      </c>
+      <c r="X22">
+        <v>417</v>
+      </c>
+      <c r="Y22">
+        <f>W22+X22+200+320</f>
+        <v>1331</v>
+      </c>
+      <c r="Z22">
+        <v>648</v>
+      </c>
+      <c r="AA22">
+        <f>Y22-Z22</f>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="109" t="s">
         <v>37</v>
       </c>
@@ -23944,7 +23973,7 @@
         <v>1891.7173209600001</v>
       </c>
     </row>
-    <row r="24" spans="1:21 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:27 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A24" s="122" t="s">
         <v>39</v>
       </c>
@@ -24014,14 +24043,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21 16384:16384" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:27 16384:16384" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A25" s="218" t="s">
         <v>84</v>
       </c>
       <c r="B25" s="219"/>
       <c r="C25" s="220">
         <f>H25/40</f>
-        <v>9.85</v>
+        <v>7.25</v>
       </c>
       <c r="D25" s="214"/>
       <c r="E25" s="214"/>
@@ -24032,11 +24061,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>21133.690000000002</v>
+        <v>16452.39</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24044,27 +24073,27 @@
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>1163.8339100000001</v>
+        <v>827.92562999999996</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>1441.1924000000004</v>
+        <v>1167.9018000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>18528.663690000001</v>
+        <v>14456.56257</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>3396.8744082000003</v>
+        <v>2663.8962066000004</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>232.44340477500003</v>
+        <v>90.401786235000003</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>22157.981502974999</v>
+        <v>17210.860562834998</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24075,7 +24104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A26" s="145"/>
       <c r="B26" s="145"/>
       <c r="C26" s="145"/>
@@ -24101,7 +24130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A27" s="145"/>
       <c r="B27" s="145"/>
       <c r="C27" s="145"/>
@@ -24127,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A28" s="145"/>
       <c r="B28" s="145"/>
       <c r="C28" s="145"/>
@@ -24153,7 +24182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A29" s="145"/>
       <c r="B29" s="145"/>
       <c r="C29" s="145"/>
@@ -24179,7 +24208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A30" s="145"/>
       <c r="B30" s="145"/>
       <c r="C30" s="145"/>
@@ -24205,7 +24234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A31" s="145"/>
       <c r="B31" s="145"/>
       <c r="C31" s="145"/>
@@ -24231,7 +24260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:27 16384:16384" ht="26" x14ac:dyDescent="0.6">
       <c r="A32" s="145"/>
       <c r="B32" s="145"/>
       <c r="C32" s="145"/>
@@ -24304,7 +24333,7 @@
       </c>
       <c r="U34" s="165">
         <f>SUM(U14:U33)</f>
-        <v>22157.981502975003</v>
+        <v>17210.860562835001</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24337,7 +24366,7 @@
       <c r="O36" s="231"/>
       <c r="P36" s="152">
         <f>I25</f>
-        <v>21133.690000000002</v>
+        <v>16452.39</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24358,7 +24387,7 @@
       <c r="O37" s="233"/>
       <c r="P37" s="153">
         <f>L25</f>
-        <v>1441.1924000000004</v>
+        <v>1167.9018000000001</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24379,7 +24408,7 @@
       <c r="O38" s="233"/>
       <c r="P38" s="154">
         <f>K25</f>
-        <v>1163.8339100000001</v>
+        <v>827.92562999999996</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24401,7 +24430,7 @@
       <c r="O39" s="233"/>
       <c r="P39" s="153">
         <f>P36-P37-P38</f>
-        <v>18528.663690000001</v>
+        <v>14456.56257</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24426,7 +24455,7 @@
       </c>
       <c r="P40" s="153">
         <f>N25</f>
-        <v>3396.8744082000003</v>
+        <v>2663.8962066000004</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24448,7 +24477,7 @@
       <c r="O41" s="235"/>
       <c r="P41" s="153">
         <f>P39+P40</f>
-        <v>21925.538098200002</v>
+        <v>17120.4587766</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24473,7 +24502,7 @@
       </c>
       <c r="P42" s="153">
         <f>O42*P41</f>
-        <v>548.13845245500011</v>
+        <v>428.01146941500002</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24483,7 +24512,7 @@
       <c r="O43" s="213"/>
       <c r="P43" s="160">
         <f>P41+P42</f>
-        <v>22473.676550655004</v>
+        <v>17548.470246015</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24663,7 +24692,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -24691,7 +24720,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -26167,7 +26196,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -26195,7 +26224,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -26829,37 +26858,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>6</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="104">
         <f>I22*8.6%</f>
-        <v>20.24268</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>203.36832000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>36.606297599999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>5.9993654400000009</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>245.97398304000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26989,36 +27016,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>20.24268</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>203.36832000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>36.606297599999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>5.9993654400000009</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>245.97398304000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27068,7 +27095,7 @@
       <c r="O28" s="231"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27089,7 +27116,7 @@
       <c r="O29" s="233"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27110,7 +27137,7 @@
       <c r="O30" s="233"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>20.24268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27132,7 +27159,7 @@
       <c r="O31" s="233"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>203.36832000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27157,7 +27184,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>36.606297599999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27179,7 +27206,7 @@
       <c r="O33" s="235"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>239.97461760000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27204,7 +27231,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>5.9993654400000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27214,7 +27241,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>245.97398304000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27386,7 +27413,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -27414,7 +27441,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -28606,7 +28633,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -28634,7 +28661,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -29268,37 +29295,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="104">
         <f>I22*8.6%</f>
-        <v>134.9512</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1355.7888000000003</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>244.04198400000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>39.99576960000001</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1639.8265536000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29428,36 +29453,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>134.9512</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1355.7888000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>244.04198400000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>39.99576960000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1639.8265536000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29507,7 +29532,7 @@
       <c r="O28" s="231"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29528,7 +29553,7 @@
       <c r="O29" s="233"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29549,7 +29574,7 @@
       <c r="O30" s="233"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>134.9512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29571,7 +29596,7 @@
       <c r="O31" s="233"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1355.7888000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29596,7 +29621,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>244.04198400000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29618,7 +29643,7 @@
       <c r="O33" s="235"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1599.8307840000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29643,7 +29668,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>39.99576960000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29653,7 +29678,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1639.8265536000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29825,7 +29850,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -29853,7 +29878,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -31044,7 +31069,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -31072,7 +31097,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -31164,7 +31189,9 @@
       <c r="A10" s="236" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="191"/>
+      <c r="B10" s="191" t="s">
+        <v>137</v>
+      </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
@@ -31187,11 +31214,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="236"/>
       <c r="B11" s="76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -31328,7 +31355,7 @@
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" s="94" t="s">
         <v>1</v>
@@ -31732,11 +31759,11 @@
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>39.99576960000001</v>
+        <v>7.9991539200000012</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1639.8265536000001</v>
+        <v>1607.8299379200002</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31891,11 +31918,11 @@
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>39.99576960000001</v>
+        <v>7.9991539200000012</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1639.8265536000001</v>
+        <v>1607.8299379200002</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -32077,11 +32104,11 @@
       </c>
       <c r="O34" s="159">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>39.99576960000001</v>
+        <v>7.9991539200000012</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32091,7 +32118,7 @@
       <c r="O35" s="213"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1639.8265536000001</v>
+        <v>1607.8299379200002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
